--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="166">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -454,10 +454,16 @@
     <t>Type d'effet indésirable</t>
   </si>
   <si>
-    <t>Type d'effet indésirable provenant du jdv-type-effet-indesirable-cisis</t>
+    <t>Type d'effet indésirable provenant du jdv-origine-effet-indesirable-cisis</t>
   </si>
   <si>
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-origine-effet-indesirable-cisis|20260619134042</t>
+  </si>
+  <si>
+    <t>fr-lm-adverse-drug-reaction.detected</t>
+  </si>
+  <si>
+    <t>Date de détection de l'effet indésirable</t>
   </si>
   <si>
     <t>fr-lm-adverse-drug-reaction.value</t>
@@ -821,7 +827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ26"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.04296875" customWidth="true" bestFit="true"/>
@@ -848,7 +854,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.90625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="56.83984375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="72.94921875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2884,7 +2890,7 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
         <v>79</v>
@@ -2899,7 +2905,7 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>145</v>
@@ -2959,7 +2965,7 @@
         <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
         <v>79</v>
@@ -2999,13 +3005,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>147</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>148</v>
-      </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3073,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3084,10 +3090,10 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>73</v>
@@ -3099,13 +3105,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="L23" t="s" s="2">
-        <v>151</v>
-      </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3156,13 +3162,13 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>73</v>
@@ -3173,10 +3179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3187,7 +3193,7 @@
         <v>74</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>73</v>
@@ -3199,7 +3205,7 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>153</v>
@@ -3235,10 +3241,10 @@
         <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>155</v>
+        <v>73</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -3256,13 +3262,13 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>73</v>
@@ -3273,10 +3279,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3284,7 +3290,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>79</v>
@@ -3302,10 +3308,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3335,10 +3341,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3356,10 +3362,10 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH25" t="s" s="2">
         <v>79</v>
@@ -3373,10 +3379,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3384,7 +3390,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3402,10 +3408,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3435,39 +3441,139 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="B27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="AA26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="AG26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH26" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="M27" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-adverse-drug-reaction.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="167">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -452,6 +452,9 @@
   </si>
   <si>
     <t>Type d'effet indésirable</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>Type d'effet indésirable provenant du jdv-origine-effet-indesirable-cisis</t>
@@ -2838,13 +2841,13 @@
         <v>73</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -2879,10 +2882,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2908,10 +2911,10 @@
         <v>127</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2962,7 +2965,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>74</v>
@@ -2979,10 +2982,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3008,10 +3011,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3062,7 +3065,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3079,10 +3082,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3105,13 +3108,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3162,7 +3165,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3179,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3205,13 +3208,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3262,7 +3265,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3279,10 +3282,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3308,10 +3311,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3338,13 +3341,13 @@
         <v>73</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3362,7 +3365,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3379,10 +3382,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3408,10 +3411,10 @@
         <v>131</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3438,13 +3441,13 @@
         <v>73</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3462,7 +3465,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -3479,10 +3482,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3508,10 +3511,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3538,13 +3541,13 @@
         <v>73</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>73</v>
@@ -3562,7 +3565,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
